--- a/Result/profitability/2388.xlsx
+++ b/Result/profitability/2388.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2062499999999998</v>
+        <v>0.1637499999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>23.1575</v>
+        <v>22.9325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06249999999999978</v>
+        <v>-0.06000000000000025</v>
       </c>
       <c r="N3" t="n">
-        <v>24.62125</v>
+        <v>24.78375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1737500000000002</v>
+        <v>-0.1450000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>27.4925</v>
+        <v>26.625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3650000000000002</v>
+        <v>-0.1887500000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>26.815</v>
+        <v>26.5875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2425000000000002</v>
+        <v>-0.2162500000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>29.40625</v>
+        <v>29.8</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-1.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3825000000000002</v>
+        <v>-0.5037500000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>32.42</v>
+        <v>32.55375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.89</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7712500000000002</v>
+        <v>-0.7500000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>35.12625</v>
+        <v>34.84625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8062500000000002</v>
+        <v>-0.8062500000000004</v>
       </c>
       <c r="N13" t="n">
         <v>42.18375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2388</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3466</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2714</v>
+      </c>
+      <c r="E75" t="n">
+        <v>753</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-338</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>473</v>
+      </c>
+      <c r="J75" t="n">
+        <v>135</v>
+      </c>
+      <c r="K75" t="n">
+        <v>141</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2837499999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.239999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09352818371607508</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.21551724137931</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07734806629834257</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
